--- a/employee_enrollment_forms/040_voluntary_health_insurance_overview--employee_enrollment_forms.xlsx
+++ b/employee_enrollment_forms/040_voluntary_health_insurance_overview--employee_enrollment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Employee Job Title</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Company Type</t>
+          <t>Company Job Type</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Job Classification</t>
+          <t>Company Job Classification</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
+          <t>Company Dob</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Date of Hire</t>
+          <t>Company Dod</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'broker'}</t>
+          <t>broker</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Broker'}</t>
+          <t>Broker</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'insurance_company'}</t>
+          <t>insurance_company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Insurance Company'}</t>
+          <t>Insurance Company</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'hr_team'}</t>
+          <t>hr_team</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'HR Team'}</t>
+          <t>HR Team</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Part-Time'}</t>
+          <t>Part-Time</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Full-Time'}</t>
+          <t>Full-Time</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'temporary'}</t>
+          <t>temporary</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Temporary'}</t>
+          <t>Temporary</t>
         </is>
       </c>
     </row>
